--- a/1.SubstitutedNitroBenzoicAcids/4C2NBA/4C2NBAA/4C2NBAA.xlsx
+++ b/1.SubstitutedNitroBenzoicAcids/4C2NBA/4C2NBAA/4C2NBAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lspri\Dropbox\Temporary Folder for Github\1.SubstitutedNitroBenzoicAcids\4C2NBAA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lspri\Documents\GitHub\CPOSS_Database\1.SubstitutedNitroBenzoicAcids\4C2NBA\4C2NBAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D79E4505-EA76-4746-B8EF-0341623D14E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B078F463-F656-4AAC-AE8E-6E9976338D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FF124D-B37B-4F82-A813-2DE1CD92039C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19F4B9B1-85A6-4C66-AA58-6656F98600AE}"/>
   </bookViews>
   <sheets>
     <sheet name="4C2NBAA_forxls" sheetId="1" r:id="rId1"/>
@@ -40,1714 +40,1714 @@
     <t>Experimental Info</t>
   </si>
   <si>
-    <t>CLNBAA_dfA159_A159</t>
+    <t>WADCOY_dfA159_A159</t>
   </si>
   <si>
     <t>A2/n</t>
   </si>
   <si>
-    <t>UNKNWN (Form I)</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfE1_E1</t>
+    <t>WADCOY (Form I)</t>
+  </si>
+  <si>
+    <t>WADCOY_dfE1_E1</t>
   </si>
   <si>
     <t>C2/c</t>
   </si>
   <si>
-    <t>UNKNWN (Form IE)</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA70_A70</t>
+    <t>WADCOY (Form IE)</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA70_A70</t>
   </si>
   <si>
     <t>P21/c</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2600_A2600</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA602_A602</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA164_A164</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA685_A685</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA316_A316</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA661_A661</t>
+    <t>WADCOY_dfA2600_A2600</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA602_A602</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA164_A164</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA685_A685</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA316_A316</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA661_A661</t>
   </si>
   <si>
     <t>P21/n</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1277_A1277</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA974_A974</t>
+    <t>WADCOY_dfA1277_A1277</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA974_A974</t>
   </si>
   <si>
     <t>Pbca</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1151_A1151</t>
+    <t>WADCOY_dfA1151_A1151</t>
   </si>
   <si>
     <t>Pc</t>
   </si>
   <si>
-    <t>CLNBAA_dfA149_A149</t>
+    <t>WADCOY_dfA149_A149</t>
   </si>
   <si>
     <t>P212121</t>
   </si>
   <si>
-    <t>CLNBAA_dfA424_A424</t>
+    <t>WADCOY_dfA424_A424</t>
   </si>
   <si>
     <t>P-1</t>
   </si>
   <si>
-    <t>CLNBAA_dfA584_A584</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1209_A1209</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA168_A168</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1940_A1940</t>
+    <t>WADCOY_dfA584_A584</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1209_A1209</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA168_A168</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1940_A1940</t>
   </si>
   <si>
     <t>P21/a</t>
   </si>
   <si>
-    <t>CLNBAA_dfA135_A135</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA315_A315</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2312_A2312</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA904_A904</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA810_A810</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA943_A943</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA346_A346</t>
+    <t>WADCOY_dfA135_A135</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA315_A315</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2312_A2312</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA904_A904</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA810_A810</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA943_A943</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA346_A346</t>
   </si>
   <si>
     <t>P21</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1423_A1423</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2971_A2971</t>
+    <t>WADCOY_dfA1423_A1423</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2971_A2971</t>
   </si>
   <si>
     <t>Pna21</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1837_A1837</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA942_A942</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA155_A155</t>
+    <t>WADCOY_dfA1837_A1837</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA942_A942</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA155_A155</t>
   </si>
   <si>
     <t>P4/n</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1886_A1886</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA540_A540</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2983_A2983</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1759_A1759</t>
+    <t>WADCOY_dfA1886_A1886</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA540_A540</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2983_A2983</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1759_A1759</t>
   </si>
   <si>
     <t>Pba2</t>
   </si>
   <si>
-    <t>CLNBAA_dfA343_A343</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1106_A1106</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1386_A1386</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1397_A1397</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA182_A182</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA746_A746</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA873_A873</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3050_A3050</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA451_A451</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA308_A308</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3170_A3170</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2295_A2295</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2288_A2288</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1288_A1288</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA499_A499</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA679_A679</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA371_A371</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2385_A2385</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1708_A1708</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2487_A2487</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA833_A833</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1768_A1768</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA571_A571</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1067_A1067</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA264_A264</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA526_A526</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA751_A751</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2868_A2868</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1459_A1459</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3133_A3133</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1890_A1890</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2289_A2289</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA633_A633</t>
+    <t>WADCOY_dfA343_A343</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1106_A1106</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1386_A1386</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1397_A1397</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA182_A182</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA746_A746</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA873_A873</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3050_A3050</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA451_A451</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA308_A308</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3170_A3170</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2295_A2295</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2288_A2288</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1288_A1288</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA499_A499</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA679_A679</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA371_A371</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2385_A2385</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1708_A1708</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2487_A2487</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA833_A833</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1768_A1768</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA571_A571</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1067_A1067</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA264_A264</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA526_A526</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA751_A751</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2868_A2868</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1459_A1459</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3133_A3133</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1890_A1890</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2289_A2289</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA633_A633</t>
   </si>
   <si>
     <t>I41/a</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3379_A3379</t>
+    <t>WADCOY_dfA3379_A3379</t>
   </si>
   <si>
     <t>P21212</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3016_A3016</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA284_A284</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2102_A2102</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA895_A895</t>
+    <t>WADCOY_dfA3016_A3016</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA284_A284</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2102_A2102</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA895_A895</t>
   </si>
   <si>
     <t>Fdd2</t>
   </si>
   <si>
-    <t>CLNBAA_dfA204_A204</t>
+    <t>WADCOY_dfA204_A204</t>
   </si>
   <si>
     <t>I-4</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3006_A3006</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2551_A2551</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA525_A525</t>
+    <t>WADCOY_dfA3006_A3006</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2551_A2551</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA525_A525</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>CLNBAA_dfA406_A406</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA769_A769</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1435_A1435</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1241_A1241</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA805_A805</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA886_A886</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3446_A3446</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2372_A2372</t>
+    <t>WADCOY_dfA406_A406</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA769_A769</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1435_A1435</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1241_A1241</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA805_A805</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA886_A886</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3446_A3446</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2372_A2372</t>
   </si>
   <si>
     <t>P-421c</t>
   </si>
   <si>
-    <t>CLNBAA_dfA638_A638</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA470_A470</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2377_A2377</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA109_A109</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2703_A2703</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2463_A2463</t>
-  </si>
-  <si>
-    <t>Aba2</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA729_A729</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1997_A1997</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3240_A3240</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3414_A3414</t>
+    <t>WADCOY_dfA638_A638</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA470_A470</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2377_A2377</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA109_A109</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2703_A2703</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2463_A2463</t>
+  </si>
+  <si>
+    <t>Aea2</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA729_A729</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1997_A1997</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3240_A3240</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3414_A3414</t>
   </si>
   <si>
     <t>I2/a</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1239_A1239</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2426_A2426</t>
+    <t>WADCOY_dfA1239_A1239</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2426_A2426</t>
   </si>
   <si>
     <t>Cc</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2160_A2160</t>
+    <t>WADCOY_dfA2160_A2160</t>
   </si>
   <si>
     <t>Pca21</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1392_A1392</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1399_A1399</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1101_A1101</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA976_A976</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2468_A2468</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA660_A660</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1480_A1480</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3003_A3003</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1317_A1317</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA946_A946</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3088_A3088</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1558_A1558</t>
+    <t>WADCOY_dfA1392_A1392</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1399_A1399</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1101_A1101</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA976_A976</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2468_A2468</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA660_A660</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1480_A1480</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3003_A3003</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1317_A1317</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA946_A946</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3088_A3088</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1558_A1558</t>
   </si>
   <si>
     <t>Pccn</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3075_A3075</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA772_A772</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3201_A3201</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1092_A1092</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA535_A535</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1496_A1496</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA220_A220</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2833_A2833</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA955_A955</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA167_A167</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2668_A2668</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2576_A2576</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA908_A908</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3451_A3451</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA93_A93</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3176_A3176</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2917_A2917</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3457_A3457</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2158_A2158</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2432_A2432</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2545_A2545</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1556_A1556</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1889_A1889</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3384_A3384</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2366_A2366</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA420_A420</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA722_A722</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1077_A1077</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1121_A1121</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2937_A2937</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2249_A2249</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2920_A2920</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1342_A1342</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA354_A354</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA933_A933</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA710_A710</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA474_A474</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3310_A3310</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2374_A2374</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA937_A937</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA658_A658</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3157_A3157</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3128_A3128</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA825_A825</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3020_A3020</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3320_A3320</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1341_A1341</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3372_A3372</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA667_A667</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3450_A3450</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1053_A1053</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2607_A2607</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2278_A2278</t>
+    <t>WADCOY_dfA3075_A3075</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA772_A772</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3201_A3201</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1092_A1092</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA535_A535</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1496_A1496</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA220_A220</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2833_A2833</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA955_A955</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA167_A167</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2668_A2668</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2576_A2576</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA908_A908</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3451_A3451</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA93_A93</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3176_A3176</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2917_A2917</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3457_A3457</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2158_A2158</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2432_A2432</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2545_A2545</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1556_A1556</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1889_A1889</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3384_A3384</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2366_A2366</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA420_A420</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA722_A722</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1077_A1077</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1121_A1121</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2937_A2937</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2249_A2249</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2920_A2920</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1342_A1342</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA354_A354</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA933_A933</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA710_A710</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA474_A474</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3310_A3310</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2374_A2374</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA937_A937</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA658_A658</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3157_A3157</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3128_A3128</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA825_A825</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3020_A3020</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3320_A3320</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1341_A1341</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3372_A3372</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA667_A667</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3450_A3450</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1053_A1053</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2607_A2607</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2278_A2278</t>
   </si>
   <si>
     <t>P21cn</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1629_A1629</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3456_A3456</t>
+    <t>WADCOY_dfA1629_A1629</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3456_A3456</t>
   </si>
   <si>
     <t>Pn</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1925_A1925</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2930_A2930</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3144_A3144</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1314_A1314</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1382_A1382</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1329_A1329</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1059_A1059</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2169_A2169</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3209_A3209</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1393_A1393</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA551_A551</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2253_A2253</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1646_A1646</t>
+    <t>WADCOY_dfA1925_A1925</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2930_A2930</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3144_A3144</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1314_A1314</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1382_A1382</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1329_A1329</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1059_A1059</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2169_A2169</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3209_A3209</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1393_A1393</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA551_A551</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2253_A2253</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1646_A1646</t>
   </si>
   <si>
     <t>P2111</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1986_A1986</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA760_A760</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA692_A692</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2625_A2625</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1513_A1513</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2744_A2744</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3213_A3213</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1785_A1785</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2384_A2384</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3231_A3231</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1442_A1442</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1731_A1731</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2649_A2649</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3521_A3521</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1497_A1497</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3162_A3162</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1224_A1224</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1522_A1522</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2342_A2342</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA604_A604</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1232_A1232</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA969_A969</t>
+    <t>WADCOY_dfA1986_A1986</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA760_A760</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA692_A692</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2625_A2625</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1513_A1513</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2744_A2744</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3213_A3213</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1785_A1785</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2384_A2384</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3231_A3231</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1442_A1442</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1731_A1731</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2649_A2649</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3521_A3521</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1497_A1497</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3162_A3162</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1224_A1224</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1522_A1522</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2342_A2342</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA604_A604</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1232_A1232</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA969_A969</t>
   </si>
   <si>
     <t>P42/n</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2326_A2326</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2718_A2718</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2641_A2641</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA758_A758</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA890_A890</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3099_A3099</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2286_A2286</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1441_A1441</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1246_A1246</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1280_A1280</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1068_A1068</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2229_A2229</t>
+    <t>WADCOY_dfA2326_A2326</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2718_A2718</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2641_A2641</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA758_A758</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA890_A890</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3099_A3099</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2286_A2286</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1441_A1441</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1246_A1246</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1280_A1280</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1068_A1068</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2229_A2229</t>
   </si>
   <si>
     <t>Aa</t>
   </si>
   <si>
-    <t>CLNBAA_dfA270_A270</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2416_A2416</t>
+    <t>WADCOY_dfA270_A270</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2416_A2416</t>
   </si>
   <si>
     <t>A2/a</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3436_A3436</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1546_A1546</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2383_A2383</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1131_A1131</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2061_A2061</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2493_A2493</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2664_A2664</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2779_A2779</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1436_A1436</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA313_A313</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1784_A1784</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3087_A3087</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2763_A2763</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1909_A1909</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1570_A1570</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2908_A2908</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2974_A2974</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1830_A1830</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2507_A2507</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3444_A3444</t>
+    <t>WADCOY_dfA3436_A3436</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1546_A1546</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2383_A2383</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1131_A1131</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2061_A2061</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2493_A2493</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2664_A2664</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2779_A2779</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1436_A1436</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA313_A313</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1784_A1784</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3087_A3087</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2763_A2763</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1909_A1909</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1570_A1570</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2908_A2908</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2974_A2974</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1830_A1830</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2507_A2507</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3444_A3444</t>
   </si>
   <si>
     <t>Cn</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2486_A2486</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2913_A2913</t>
+    <t>WADCOY_dfA2486_A2486</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2913_A2913</t>
   </si>
   <si>
     <t>I2/c</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1874_A1874</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3022_A3022</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1861_A1861</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1710_A1710</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1406_A1406</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA570_A570</t>
+    <t>WADCOY_dfA1874_A1874</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3022_A3022</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1861_A1861</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1710_A1710</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1406_A1406</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA570_A570</t>
   </si>
   <si>
     <t>R-3</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3390_A3390</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2601_A2601</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2436_A2436</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3064_A3064</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2975_A2975</t>
+    <t>WADCOY_dfA3390_A3390</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2601_A2601</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2436_A2436</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3064_A3064</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2975_A2975</t>
   </si>
   <si>
     <t>C2/n</t>
   </si>
   <si>
-    <t>CLNBAA_dfA1474_A1474</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3413_A3413</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3251_A3251</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3468_A3468</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2852_A2852</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3007_A3007</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3405_A3405</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2831_A2831</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1508_A1508</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2351_A2351</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2758_A2758</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1694_A1694</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3234_A3234</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2800_A2800</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2921_A2921</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2399_A2399</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1478_A1478</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2688_A2688</t>
+    <t>WADCOY_dfA1474_A1474</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3413_A3413</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3251_A3251</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3468_A3468</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2852_A2852</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3007_A3007</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3405_A3405</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2831_A2831</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1508_A1508</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2351_A2351</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2758_A2758</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1694_A1694</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3234_A3234</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2800_A2800</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2921_A2921</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2399_A2399</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1478_A1478</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2688_A2688</t>
   </si>
   <si>
     <t>P61</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2506_A2506</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1882_A1882</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2880_A2880</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1639_A1639</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3101_A3101</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1098_A1098</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2861_A2861</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2090_A2090</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2211_A2211</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3230_A3230</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1120_A1120</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2164_A2164</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2397_A2397</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA877_A877</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2409_A2409</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2023_A2023</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3370_A3370</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA968_A968</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1031_A1031</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2702_A2702</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2531_A2531</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2043_A2043</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2968_A2968</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2748_A2748</t>
+    <t>WADCOY_dfA2506_A2506</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1882_A1882</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2880_A2880</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1639_A1639</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3101_A3101</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1098_A1098</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2861_A2861</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2090_A2090</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2211_A2211</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3230_A3230</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1120_A1120</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2164_A2164</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2397_A2397</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA877_A877</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2409_A2409</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2023_A2023</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3370_A3370</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA968_A968</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1031_A1031</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2702_A2702</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2531_A2531</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2043_A2043</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2968_A2968</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2748_A2748</t>
   </si>
   <si>
     <t>Pbcn</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3501_A3501</t>
+    <t>WADCOY_dfA3501_A3501</t>
   </si>
   <si>
     <t>P2/a</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2829_A2829</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1150_A1150</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1340_A1340</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2905_A2905</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1446_A1446</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1971_A1971</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2657_A2657</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2780_A2780</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2499_A2499</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2604_A2604</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3394_A3394</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA789_A789</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1780_A1780</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3348_A3348</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1966_A1966</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1990_A1990</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3340_A3340</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2185_A2185</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3406_A3406</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1108_A1108</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2132_A2132</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2838_A2838</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1732_A1732</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2845_A2845</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2885_A2885</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2173_A2173</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1291_A1291</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2834_A2834</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2722_A2722</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3527_A3527</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3159_A3159</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA966_A966</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1787_A1787</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3513_A3513</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2357_A2357</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3089_A3089</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1486_A1486</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2812_A2812</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2356_A2356</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1402_A1402</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2307_A2307</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA630_A630</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3463_A3463</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3215_A3215</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1999_A1999</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3012_A3012</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2853_A2853</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3048_A3048</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3052_A3052</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2328_A2328</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2141_A2141</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1123_A1123</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2446_A2446</t>
+    <t>WADCOY_dfA2829_A2829</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1150_A1150</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1340_A1340</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2905_A2905</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1446_A1446</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1971_A1971</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2657_A2657</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2780_A2780</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2499_A2499</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2604_A2604</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3394_A3394</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA789_A789</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1780_A1780</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3348_A3348</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1966_A1966</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1990_A1990</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3340_A3340</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2185_A2185</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3406_A3406</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1108_A1108</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2132_A2132</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2838_A2838</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1732_A1732</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2845_A2845</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2885_A2885</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2173_A2173</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1291_A1291</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2834_A2834</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2722_A2722</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3527_A3527</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3159_A3159</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA966_A966</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1787_A1787</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3513_A3513</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2357_A2357</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3089_A3089</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1486_A1486</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2812_A2812</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2356_A2356</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1402_A1402</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2307_A2307</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA630_A630</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3463_A3463</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3215_A3215</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1999_A1999</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3012_A3012</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2853_A2853</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3048_A3048</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3052_A3052</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2328_A2328</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2141_A2141</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1123_A1123</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2446_A2446</t>
   </si>
   <si>
     <t>Iba2</t>
   </si>
   <si>
-    <t>CLNBAA_dfA151_A151</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3015_A3015</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3001_A3001</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2150_A2150</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2699_A2699</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2218_A2218</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1908_A1908</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1859_A1859</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2004_A2004</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2323_A2323</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2073_A2073</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3305_A3305</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3346_A3346</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2318_A2318</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA768_A768</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3066_A3066</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3034_A3034</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3290_A3290</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2387_A2387</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1135_A1135</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2693_A2693</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1047_A1047</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2338_A2338</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2796_A2796</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3043_A3043</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3117_A3117</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1378_A1378</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2524_A2524</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3424_A3424</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2358_A2358</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3049_A3049</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2118_A2118</t>
+    <t>WADCOY_dfA151_A151</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3015_A3015</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3001_A3001</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2150_A2150</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2699_A2699</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2218_A2218</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1908_A1908</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1859_A1859</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2004_A2004</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2323_A2323</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2073_A2073</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3305_A3305</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3346_A3346</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2318_A2318</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA768_A768</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3066_A3066</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3034_A3034</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3290_A3290</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2387_A2387</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1135_A1135</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2693_A2693</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1047_A1047</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2338_A2338</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2796_A2796</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3043_A3043</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3117_A3117</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1378_A1378</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2524_A2524</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3424_A3424</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2358_A2358</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3049_A3049</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2118_A2118</t>
   </si>
   <si>
     <t>C2</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3420_A3420</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2754_A2754</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2392_A2392</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3462_A3462</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3490_A3490</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1410_A1410</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1019_A1019</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2850_A2850</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2950_A2950</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3294_A3294</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1998_A1998</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1822_A1822</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3459_A3459</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA889_A889</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3250_A3250</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3134_A3134</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2797_A2797</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2648_A2648</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1445_A1445</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2995_A2995</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2809_A2809</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA786_A786</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1813_A1813</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3161_A3161</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1299_A1299</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1816_A1816</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3274_A3274</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2893_A2893</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2612_A2612</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3329_A3329</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3401_A3401</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2676_A2676</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3418_A3418</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2958_A2958</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3223_A3223</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2783_A2783</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1484_A1484</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1250_A1250</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2133_A2133</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA845_A845</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3217_A3217</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1747_A1747</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3187_A3187</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1033_A1033</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3333_A3333</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1982_A1982</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2786_A2786</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2417_A2417</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3298_A3298</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2081_A2081</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3511_A3511</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3345_A3345</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1674_A1674</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1894_A1894</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2647_A2647</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3074_A3074</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3267_A3267</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2740_A2740</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3035_A3035</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3302_A3302</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2492_A2492</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2904_A2904</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3121_A3121</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2455_A2455</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3437_A3437</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3330_A3330</t>
+    <t>WADCOY_dfA3420_A3420</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2754_A2754</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2392_A2392</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3462_A3462</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3490_A3490</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1410_A1410</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1019_A1019</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2850_A2850</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2950_A2950</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3294_A3294</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1998_A1998</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1822_A1822</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3459_A3459</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA889_A889</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3250_A3250</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3134_A3134</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2797_A2797</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2648_A2648</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1445_A1445</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2995_A2995</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2809_A2809</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA786_A786</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1813_A1813</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3161_A3161</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1299_A1299</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1816_A1816</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3274_A3274</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2893_A2893</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2612_A2612</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3329_A3329</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3401_A3401</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2676_A2676</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3418_A3418</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2958_A2958</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3223_A3223</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2783_A2783</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1484_A1484</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1250_A1250</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2133_A2133</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA845_A845</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3217_A3217</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1747_A1747</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3187_A3187</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1033_A1033</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3333_A3333</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1982_A1982</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2786_A2786</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2417_A2417</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3298_A3298</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2081_A2081</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3511_A3511</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3345_A3345</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1674_A1674</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1894_A1894</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2647_A2647</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3074_A3074</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3267_A3267</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2740_A2740</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3035_A3035</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3302_A3302</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2492_A2492</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2904_A2904</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3121_A3121</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2455_A2455</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3437_A3437</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3330_A3330</t>
   </si>
   <si>
     <t>R3c</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3432_A3432</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2168_A2168</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2724_A2724</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3316_A3316</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2256_A2256</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2864_A2864</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1721_A1721</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3429_A3429</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2476_A2476</t>
+    <t>WADCOY_dfA3432_A3432</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2168_A2168</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2724_A2724</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3316_A3316</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2256_A2256</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2864_A2864</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1721_A1721</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3429_A3429</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2476_A2476</t>
   </si>
   <si>
     <t>R-3c</t>
   </si>
   <si>
-    <t>CLNBAA_dfA3496_A3496</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1814_A1814</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3081_A3081</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2610_A2610</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2495_A2495</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3062_A3062</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1598_A1598</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3313_A3313</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2415_A2415</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2379_A2379</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2751_A2751</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1664_A1664</t>
+    <t>WADCOY_dfA3496_A3496</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1814_A1814</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3081_A3081</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2610_A2610</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2495_A2495</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3062_A3062</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1598_A1598</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3313_A3313</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2415_A2415</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2379_A2379</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2751_A2751</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1664_A1664</t>
   </si>
   <si>
     <t>P43212</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2435_A2435</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2644_A2644</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2094_A2094</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2884_A2884</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3514_A3514</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2543_A2543</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2329_A2329</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2923_A2923</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2646_A2646</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2696_A2696</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2730_A2730</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2946_A2946</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2804_A2804</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2375_A2375</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2658_A2658</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2731_A2731</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2980_A2980</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2345_A2345</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3454_A3454</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3269_A3269</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1750_A1750</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2055_A2055</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2674_A2674</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2891_A2891</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA909_A909</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1700_A1700</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3238_A3238</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3106_A3106</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3498_A3498</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2772_A2772</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3248_A3248</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3063_A3063</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2016_A2016</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3167_A3167</t>
+    <t>WADCOY_dfA2435_A2435</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2644_A2644</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2094_A2094</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2884_A2884</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3514_A3514</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2543_A2543</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2329_A2329</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2923_A2923</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2646_A2646</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2696_A2696</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2730_A2730</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2946_A2946</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2804_A2804</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2375_A2375</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2658_A2658</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2731_A2731</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2980_A2980</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2345_A2345</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3454_A3454</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3269_A3269</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1750_A1750</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2055_A2055</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2674_A2674</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2891_A2891</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA909_A909</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1700_A1700</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3238_A3238</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3106_A3106</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3498_A3498</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2772_A2772</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3248_A3248</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3063_A3063</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2016_A2016</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3167_A3167</t>
   </si>
   <si>
     <t>Ia</t>
   </si>
   <si>
-    <t>CLNBAA_dfA2105_A2105</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2365_A2365</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2816_A2816</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2721_A2721</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2368_A2368</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2064_A2064</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3038_A3038</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3164_A3164</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2906_A2906</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA793_A793</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2367_A2367</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2982_A2982</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2624_A2624</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2473_A2473</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3025_A3025</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2734_A2734</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3358_A3358</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2814_A2814</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3002_A3002</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2496_A2496</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2986_A2986</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2530_A2530</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2230_A2230</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA1563_A1563</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2424_A2424</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3452_A3452</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA853_A853</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA3478_A3478</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA513_A513</t>
-  </si>
-  <si>
-    <t>CLNBAA_dfA2899_A2899</t>
+    <t>WADCOY_dfA2105_A2105</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2365_A2365</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2816_A2816</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2721_A2721</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2368_A2368</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2064_A2064</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3038_A3038</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3164_A3164</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2906_A2906</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA793_A793</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2367_A2367</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2982_A2982</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2624_A2624</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2473_A2473</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3025_A3025</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2734_A2734</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3358_A3358</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2814_A2814</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3002_A3002</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2496_A2496</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2986_A2986</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2530_A2530</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2230_A2230</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA1563_A1563</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2424_A2424</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3452_A3452</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA853_A853</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA3478_A3478</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA513_A513</t>
+  </si>
+  <si>
+    <t>WADCOY_dfA2899_A2899</t>
   </si>
 </sst>
 </file>
@@ -2607,7 +2607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A9D9353-1993-4F1B-9C73-1F34ACED2BA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B5766E-8E64-4EFA-96CF-9900D9E321A7}">
   <dimension ref="A1:F526"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2659,8 +2659,7 @@
         <v>1.6826000000000001</v>
       </c>
       <c r="C3">
-        <f>-113.25 -113.25</f>
-        <v>-226.5</v>
+        <v>-113.25</v>
       </c>
       <c r="D3">
         <v>0.72623599999999999</v>
